--- a/Pruebas calificadas/COLEGIO ATABANZA 503_Ajustado_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO ATABANZA 503_Ajustado_CALIFICADO.xlsx
@@ -825,7 +825,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>1206221011</t>
+          <t>1140929606</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>1206221011</t>
+          <t>1140929606</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
